--- a/data/processed/plant_kpi_report.xlsx
+++ b/data/processed/plant_kpi_report.xlsx
@@ -432,67 +432,51 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>total_qty</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>total_revenue</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>total_customer_mix_cost</t>
-        </is>
-      </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>total_optimized_mix_cost</t>
+          <t>avg_selling_price</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>total_savings</t>
+          <t>avg_c1</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>avg_savings_per_cum</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>savings_per_cum</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>total_qty</t>
+          <t>avg_saving_per_cum</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
+        <v>4433.5</v>
+      </c>
+      <c r="B2" t="n">
         <v>25716856.09</v>
       </c>
-      <c r="B2" t="n">
-        <v>16281290.13705</v>
-      </c>
       <c r="C2" t="n">
-        <v>14886512.22177591</v>
+        <v>5800.576539979701</v>
       </c>
       <c r="D2" t="n">
-        <v>1394777.915274089</v>
+        <v>2128.243138141424</v>
       </c>
       <c r="E2" t="n">
-        <v>302.9152437592445</v>
-      </c>
-      <c r="F2" t="n">
-        <v>1394777.915274089</v>
-      </c>
-      <c r="G2" t="n">
-        <v>4433.5</v>
+        <v>314.5997327786375</v>
       </c>
     </row>
   </sheetData>
@@ -506,7 +490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H55"/>
+  <dimension ref="A1:F55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -527,27 +511,17 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>total_customer_mix_cost</t>
+          <t>avg_asp</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>total_optimized_mix_cost</t>
+          <t>avg_c1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>total_savings</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>avg_savings_per_cum</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>savings_per_cum</t>
+          <t>avg_saving_per_cum</t>
         </is>
       </c>
     </row>
@@ -564,19 +538,13 @@
         <v>307800</v>
       </c>
       <c r="D2" t="n">
-        <v>206368.56</v>
+        <v>5700</v>
       </c>
       <c r="E2" t="n">
-        <v>196421.3373176471</v>
+        <v>1878.36</v>
       </c>
       <c r="F2" t="n">
-        <v>9947.222682352942</v>
-      </c>
-      <c r="G2" t="n">
         <v>184.2078274509804</v>
-      </c>
-      <c r="H2" t="n">
-        <v>9947.222682352942</v>
       </c>
     </row>
     <row r="3">
@@ -592,19 +560,13 @@
         <v>598950</v>
       </c>
       <c r="D3" t="n">
-        <v>385329.2145</v>
+        <v>5185.714285714285</v>
       </c>
       <c r="E3" t="n">
-        <v>343425.44578</v>
+        <v>1849.53061038961</v>
       </c>
       <c r="F3" t="n">
-        <v>41903.76872000001</v>
-      </c>
-      <c r="G3" t="n">
-        <v>333.1214954335778</v>
-      </c>
-      <c r="H3" t="n">
-        <v>41903.76872000001</v>
+        <v>362.8031923809525</v>
       </c>
     </row>
     <row r="4">
@@ -620,19 +582,13 @@
         <v>1722600</v>
       </c>
       <c r="D4" t="n">
-        <v>1072495.0368</v>
+        <v>5800</v>
       </c>
       <c r="E4" t="n">
-        <v>1002299.948628659</v>
+        <v>2188.905600000001</v>
       </c>
       <c r="F4" t="n">
-        <v>70195.08817134057</v>
-      </c>
-      <c r="G4" t="n">
-        <v>162.2161088528212</v>
-      </c>
-      <c r="H4" t="n">
-        <v>70195.08817134058</v>
+        <v>236.347098220002</v>
       </c>
     </row>
     <row r="5">
@@ -648,19 +604,13 @@
         <v>122900</v>
       </c>
       <c r="D5" t="n">
-        <v>73799.4754</v>
+        <v>5716.279069767442</v>
       </c>
       <c r="E5" t="n">
-        <v>68738.07664411765</v>
+        <v>2283.745330232558</v>
       </c>
       <c r="F5" t="n">
-        <v>5061.398755882348</v>
-      </c>
-      <c r="G5" t="n">
-        <v>225.9374297385619</v>
-      </c>
-      <c r="H5" t="n">
-        <v>5061.398755882348</v>
+        <v>235.4138956224348</v>
       </c>
     </row>
     <row r="6">
@@ -676,19 +626,13 @@
         <v>249400</v>
       </c>
       <c r="D6" t="n">
-        <v>148439.5604</v>
+        <v>5800</v>
       </c>
       <c r="E6" t="n">
-        <v>134700.3764958791</v>
+        <v>2347.9172</v>
       </c>
       <c r="F6" t="n">
-        <v>13739.18390412089</v>
-      </c>
-      <c r="G6" t="n">
-        <v>240.713514239927</v>
-      </c>
-      <c r="H6" t="n">
-        <v>13739.18390412089</v>
+        <v>319.5159047469974</v>
       </c>
     </row>
     <row r="7">
@@ -704,19 +648,13 @@
         <v>148800</v>
       </c>
       <c r="D7" t="n">
-        <v>101410.92</v>
+        <v>6200</v>
       </c>
       <c r="E7" t="n">
-        <v>90867.6479</v>
+        <v>1974.545</v>
       </c>
       <c r="F7" t="n">
-        <v>10543.2721</v>
-      </c>
-      <c r="G7" t="n">
         <v>439.3030041666666</v>
-      </c>
-      <c r="H7" t="n">
-        <v>10543.2721</v>
       </c>
     </row>
     <row r="8">
@@ -732,19 +670,13 @@
         <v>156800</v>
       </c>
       <c r="D8" t="n">
-        <v>96658.3184</v>
+        <v>5600</v>
       </c>
       <c r="E8" t="n">
-        <v>88411.58490131614</v>
+        <v>2147.9172</v>
       </c>
       <c r="F8" t="n">
-        <v>8246.733498683869</v>
-      </c>
-      <c r="G8" t="n">
-        <v>294.5261963815667</v>
-      </c>
-      <c r="H8" t="n">
-        <v>8246.733498683869</v>
+        <v>294.5261963815668</v>
       </c>
     </row>
     <row r="9">
@@ -760,19 +692,13 @@
         <v>179950</v>
       </c>
       <c r="D9" t="n">
-        <v>105288.5254</v>
+        <v>5900</v>
       </c>
       <c r="E9" t="n">
-        <v>97993.28109620567</v>
+        <v>2447.917199999999</v>
       </c>
       <c r="F9" t="n">
-        <v>7295.244303794336</v>
-      </c>
-      <c r="G9" t="n">
-        <v>225.1504323286055</v>
-      </c>
-      <c r="H9" t="n">
-        <v>7295.244303794336</v>
+        <v>239.1883378293225</v>
       </c>
     </row>
     <row r="10">
@@ -788,19 +714,13 @@
         <v>2102650</v>
       </c>
       <c r="D10" t="n">
-        <v>1331320.0966</v>
+        <v>5808.425414364641</v>
       </c>
       <c r="E10" t="n">
-        <v>1211525.539318243</v>
+        <v>2130.745589502762</v>
       </c>
       <c r="F10" t="n">
-        <v>119794.5572817575</v>
-      </c>
-      <c r="G10" t="n">
-        <v>269.4329529101288</v>
-      </c>
-      <c r="H10" t="n">
-        <v>119794.5572817574</v>
+        <v>330.9241913860703</v>
       </c>
     </row>
     <row r="11">
@@ -816,19 +736,13 @@
         <v>184321.97</v>
       </c>
       <c r="D11" t="n">
-        <v>116683.965</v>
+        <v>6355.93</v>
       </c>
       <c r="E11" t="n">
-        <v>102936.7850409091</v>
+        <v>2332.345</v>
       </c>
       <c r="F11" t="n">
-        <v>13747.17995909091</v>
-      </c>
-      <c r="G11" t="n">
-        <v>474.3457757575759</v>
-      </c>
-      <c r="H11" t="n">
-        <v>13747.17995909091</v>
+        <v>474.0406882445142</v>
       </c>
     </row>
     <row r="12">
@@ -844,19 +758,13 @@
         <v>1464975</v>
       </c>
       <c r="D12" t="n">
-        <v>903500.0206</v>
+        <v>5756.286836935167</v>
       </c>
       <c r="E12" t="n">
-        <v>819578.0752420879</v>
+        <v>2206.188524165029</v>
       </c>
       <c r="F12" t="n">
-        <v>83921.94535791218</v>
-      </c>
-      <c r="G12" t="n">
-        <v>329.904446468361</v>
-      </c>
-      <c r="H12" t="n">
-        <v>83921.94535791218</v>
+        <v>329.7522410919929</v>
       </c>
     </row>
     <row r="13">
@@ -872,19 +780,13 @@
         <v>52950</v>
       </c>
       <c r="D13" t="n">
-        <v>32013.2002</v>
+        <v>5573.684210526316</v>
       </c>
       <c r="E13" t="n">
-        <v>29839.39493913043</v>
+        <v>2203.873663157895</v>
       </c>
       <c r="F13" t="n">
-        <v>2173.805260869566</v>
-      </c>
-      <c r="G13" t="n">
-        <v>251.3572407608697</v>
-      </c>
-      <c r="H13" t="n">
-        <v>2173.805260869566</v>
+        <v>228.8216064073227</v>
       </c>
     </row>
     <row r="14">
@@ -900,19 +802,13 @@
         <v>169400</v>
       </c>
       <c r="D14" t="n">
-        <v>114345.028</v>
+        <v>6050</v>
       </c>
       <c r="E14" t="n">
-        <v>103129.2613</v>
+        <v>1966.249</v>
       </c>
       <c r="F14" t="n">
-        <v>11215.76669999999</v>
-      </c>
-      <c r="G14" t="n">
         <v>400.563096428571</v>
-      </c>
-      <c r="H14" t="n">
-        <v>11215.76669999999</v>
       </c>
     </row>
     <row r="15">
@@ -928,19 +824,13 @@
         <v>46400</v>
       </c>
       <c r="D15" t="n">
-        <v>27616.6624</v>
+        <v>5800</v>
       </c>
       <c r="E15" t="n">
-        <v>25372.48314545455</v>
+        <v>2347.9172</v>
       </c>
       <c r="F15" t="n">
-        <v>2244.179254545455</v>
-      </c>
-      <c r="G15" t="n">
         <v>280.5224068181819</v>
-      </c>
-      <c r="H15" t="n">
-        <v>2244.179254545455</v>
       </c>
     </row>
     <row r="16">
@@ -956,19 +846,13 @@
         <v>727100</v>
       </c>
       <c r="D16" t="n">
-        <v>426233.988</v>
+        <v>5702.745098039216</v>
       </c>
       <c r="E16" t="n">
-        <v>391600.0478766939</v>
+        <v>2359.73342745098</v>
       </c>
       <c r="F16" t="n">
-        <v>34633.94012330614</v>
-      </c>
-      <c r="G16" t="n">
-        <v>266.3070914532967</v>
-      </c>
-      <c r="H16" t="n">
-        <v>34633.94012330614</v>
+        <v>271.6387460651462</v>
       </c>
     </row>
     <row r="17">
@@ -984,19 +868,13 @@
         <v>253700</v>
       </c>
       <c r="D17" t="n">
-        <v>162897.029</v>
+        <v>5900</v>
       </c>
       <c r="E17" t="n">
-        <v>148661.6434</v>
+        <v>2111.697</v>
       </c>
       <c r="F17" t="n">
-        <v>14235.38559999998</v>
-      </c>
-      <c r="G17" t="n">
-        <v>319.0069198067628</v>
-      </c>
-      <c r="H17" t="n">
-        <v>14235.38559999998</v>
+        <v>331.055479069767</v>
       </c>
     </row>
     <row r="18">
@@ -1012,19 +890,13 @@
         <v>40600</v>
       </c>
       <c r="D18" t="n">
-        <v>25634.2436</v>
+        <v>5800</v>
       </c>
       <c r="E18" t="n">
-        <v>21955.02254814815</v>
+        <v>2137.9652</v>
       </c>
       <c r="F18" t="n">
-        <v>3679.221051851852</v>
-      </c>
-      <c r="G18" t="n">
         <v>525.6030074074074</v>
-      </c>
-      <c r="H18" t="n">
-        <v>3679.221051851852</v>
       </c>
     </row>
     <row r="19">
@@ -1040,19 +912,13 @@
         <v>226800</v>
       </c>
       <c r="D19" t="n">
-        <v>126146.3196</v>
+        <v>5400</v>
       </c>
       <c r="E19" t="n">
-        <v>110840.3795</v>
+        <v>2396.5162</v>
       </c>
       <c r="F19" t="n">
-        <v>15305.94010000003</v>
-      </c>
-      <c r="G19" t="n">
         <v>364.4271452380958</v>
-      </c>
-      <c r="H19" t="n">
-        <v>15305.94010000003</v>
       </c>
     </row>
     <row r="20">
@@ -1068,19 +934,13 @@
         <v>34125</v>
       </c>
       <c r="D20" t="n">
-        <v>19522.6447</v>
+        <v>5250</v>
       </c>
       <c r="E20" t="n">
-        <v>17182.458</v>
+        <v>2246.5162</v>
       </c>
       <c r="F20" t="n">
-        <v>2340.186700000003</v>
-      </c>
-      <c r="G20" t="n">
         <v>360.0287230769236</v>
-      </c>
-      <c r="H20" t="n">
-        <v>2340.186700000003</v>
       </c>
     </row>
     <row r="21">
@@ -1096,19 +956,13 @@
         <v>31500</v>
       </c>
       <c r="D21" t="n">
-        <v>20399.1745</v>
+        <v>6300</v>
       </c>
       <c r="E21" t="n">
-        <v>16666.70356666667</v>
+        <v>2220.1651</v>
       </c>
       <c r="F21" t="n">
-        <v>3732.470933333334</v>
-      </c>
-      <c r="G21" t="n">
         <v>746.4941866666668</v>
-      </c>
-      <c r="H21" t="n">
-        <v>3732.470933333334</v>
       </c>
     </row>
     <row r="22">
@@ -1124,19 +978,13 @@
         <v>45050</v>
       </c>
       <c r="D22" t="n">
-        <v>25529.6123</v>
+        <v>5300</v>
       </c>
       <c r="E22" t="n">
-        <v>22537.26772307692</v>
+        <v>2296.5162</v>
       </c>
       <c r="F22" t="n">
-        <v>2992.344576923083</v>
-      </c>
-      <c r="G22" t="n">
         <v>352.0405384615392</v>
-      </c>
-      <c r="H22" t="n">
-        <v>2992.344576923083</v>
       </c>
     </row>
     <row r="23">
@@ -1152,19 +1000,13 @@
         <v>116600</v>
       </c>
       <c r="D23" t="n">
-        <v>71647.09640000001</v>
+        <v>5300</v>
       </c>
       <c r="E23" t="n">
-        <v>63301.85627586208</v>
+        <v>2043.3138</v>
       </c>
       <c r="F23" t="n">
-        <v>8345.240124137927</v>
-      </c>
-      <c r="G23" t="n">
-        <v>379.329096551724</v>
-      </c>
-      <c r="H23" t="n">
-        <v>8345.240124137927</v>
+        <v>379.3290965517239</v>
       </c>
     </row>
     <row r="24">
@@ -1180,19 +1022,13 @@
         <v>92125.44</v>
       </c>
       <c r="D24" t="n">
-        <v>43528.2168</v>
+        <v>7677.12</v>
       </c>
       <c r="E24" t="n">
-        <v>39134.83340000001</v>
+        <v>4049.7686</v>
       </c>
       <c r="F24" t="n">
-        <v>4393.383399999992</v>
-      </c>
-      <c r="G24" t="n">
         <v>366.1152833333326</v>
-      </c>
-      <c r="H24" t="n">
-        <v>4393.383399999986</v>
       </c>
     </row>
     <row r="25">
@@ -1208,19 +1044,13 @@
         <v>660800</v>
       </c>
       <c r="D25" t="n">
-        <v>386633.2736</v>
+        <v>5900</v>
       </c>
       <c r="E25" t="n">
-        <v>363450.8003833279</v>
+        <v>2447.9172</v>
       </c>
       <c r="F25" t="n">
-        <v>23182.47321667217</v>
-      </c>
-      <c r="G25" t="n">
-        <v>200.5559386054667</v>
-      </c>
-      <c r="H25" t="n">
-        <v>23182.47321667217</v>
+        <v>206.9863680060015</v>
       </c>
     </row>
     <row r="26">
@@ -1236,19 +1066,13 @@
         <v>84000</v>
       </c>
       <c r="D26" t="n">
-        <v>58183.328</v>
+        <v>6000</v>
       </c>
       <c r="E26" t="n">
-        <v>48415.58211172248</v>
+        <v>1844.048</v>
       </c>
       <c r="F26" t="n">
-        <v>9767.745888277515</v>
-      </c>
-      <c r="G26" t="n">
-        <v>677.0843867224883</v>
-      </c>
-      <c r="H26" t="n">
-        <v>9767.745888277515</v>
+        <v>697.6961348769654</v>
       </c>
     </row>
     <row r="27">
@@ -1264,19 +1088,13 @@
         <v>64200</v>
       </c>
       <c r="D27" t="n">
-        <v>41219.928</v>
+        <v>5350</v>
       </c>
       <c r="E27" t="n">
-        <v>38241.8625509434</v>
+        <v>1915.006</v>
       </c>
       <c r="F27" t="n">
-        <v>2978.065449056599</v>
-      </c>
-      <c r="G27" t="n">
         <v>248.1721207547166</v>
-      </c>
-      <c r="H27" t="n">
-        <v>2978.065449056599</v>
       </c>
     </row>
     <row r="28">
@@ -1292,19 +1110,13 @@
         <v>711200</v>
       </c>
       <c r="D28" t="n">
-        <v>438414.5156</v>
+        <v>5600</v>
       </c>
       <c r="E28" t="n">
-        <v>417279.5065415027</v>
+        <v>2147.9172</v>
       </c>
       <c r="F28" t="n">
-        <v>21135.00905849731</v>
-      </c>
-      <c r="G28" t="n">
-        <v>159.2130666555989</v>
-      </c>
-      <c r="H28" t="n">
-        <v>21135.00905849731</v>
+        <v>166.4173941613961</v>
       </c>
     </row>
     <row r="29">
@@ -1320,19 +1132,13 @@
         <v>109150</v>
       </c>
       <c r="D29" t="n">
-        <v>63863.5318</v>
+        <v>5900</v>
       </c>
       <c r="E29" t="n">
-        <v>61473.9727</v>
+        <v>2447.9172</v>
       </c>
       <c r="F29" t="n">
-        <v>2389.559100000002</v>
-      </c>
-      <c r="G29" t="n">
         <v>129.1653567567569</v>
-      </c>
-      <c r="H29" t="n">
-        <v>2389.559100000002</v>
       </c>
     </row>
     <row r="30">
@@ -1348,19 +1154,13 @@
         <v>1509400</v>
       </c>
       <c r="D30" t="n">
-        <v>917009.5109</v>
+        <v>6049.699398797595</v>
       </c>
       <c r="E30" t="n">
-        <v>876036.6284346757</v>
+        <v>2374.31057755511</v>
       </c>
       <c r="F30" t="n">
-        <v>40972.88246532429</v>
-      </c>
-      <c r="G30" t="n">
-        <v>171.1684255029959</v>
-      </c>
-      <c r="H30" t="n">
-        <v>40972.88246532429</v>
+        <v>164.219969800899</v>
       </c>
     </row>
     <row r="31">
@@ -1376,19 +1176,13 @@
         <v>3153800</v>
       </c>
       <c r="D31" t="n">
-        <v>2129574.908</v>
+        <v>5928.195488721804</v>
       </c>
       <c r="E31" t="n">
-        <v>1961906.49710912</v>
+        <v>1925.235135338346</v>
       </c>
       <c r="F31" t="n">
-        <v>167668.41089088</v>
-      </c>
-      <c r="G31" t="n">
-        <v>292.90308917752</v>
-      </c>
-      <c r="H31" t="n">
-        <v>167668.41089088</v>
+        <v>315.1661858851128</v>
       </c>
     </row>
     <row r="32">
@@ -1404,19 +1198,13 @@
         <v>142500</v>
       </c>
       <c r="D32" t="n">
-        <v>92714.27499999999</v>
+        <v>5700</v>
       </c>
       <c r="E32" t="n">
-        <v>88686.37096153849</v>
+        <v>1991.429</v>
       </c>
       <c r="F32" t="n">
-        <v>4027.904038461509</v>
-      </c>
-      <c r="G32" t="n">
         <v>161.1161615384603</v>
-      </c>
-      <c r="H32" t="n">
-        <v>4027.904038461509</v>
       </c>
     </row>
     <row r="33">
@@ -1432,19 +1220,13 @@
         <v>538650</v>
       </c>
       <c r="D33" t="n">
-        <v>350459.9595</v>
+        <v>5700</v>
       </c>
       <c r="E33" t="n">
-        <v>327753.7231798451</v>
+        <v>1991.429</v>
       </c>
       <c r="F33" t="n">
-        <v>22706.23632015493</v>
-      </c>
-      <c r="G33" t="n">
-        <v>218.17392118863</v>
-      </c>
-      <c r="H33" t="n">
-        <v>22706.23632015493</v>
+        <v>240.2776330175125</v>
       </c>
     </row>
     <row r="34">
@@ -1460,19 +1242,13 @@
         <v>31200</v>
       </c>
       <c r="D34" t="n">
-        <v>19540.1172</v>
+        <v>5200</v>
       </c>
       <c r="E34" t="n">
-        <v>17222.0853</v>
+        <v>1943.3138</v>
       </c>
       <c r="F34" t="n">
-        <v>2318.031899999998</v>
-      </c>
-      <c r="G34" t="n">
         <v>386.3386499999997</v>
-      </c>
-      <c r="H34" t="n">
-        <v>2318.031899999998</v>
       </c>
     </row>
     <row r="35">
@@ -1488,19 +1264,13 @@
         <v>364500</v>
       </c>
       <c r="D35" t="n">
-        <v>233015.589</v>
+        <v>5400</v>
       </c>
       <c r="E35" t="n">
-        <v>210983.603057967</v>
+        <v>1947.9172</v>
       </c>
       <c r="F35" t="n">
-        <v>22031.98594203297</v>
-      </c>
-      <c r="G35" t="n">
-        <v>240.7135142399268</v>
-      </c>
-      <c r="H35" t="n">
-        <v>22031.98594203297</v>
+        <v>326.3997917338218</v>
       </c>
     </row>
     <row r="36">
@@ -1516,19 +1286,13 @@
         <v>166312.5</v>
       </c>
       <c r="D36" t="n">
-        <v>110475.6165</v>
+        <v>5117.307692307692</v>
       </c>
       <c r="E36" t="n">
-        <v>99619.92880179905</v>
+        <v>1718.057953846154</v>
       </c>
       <c r="F36" t="n">
-        <v>10855.68769820096</v>
-      </c>
-      <c r="G36" t="n">
-        <v>259.6144357430159</v>
-      </c>
-      <c r="H36" t="n">
-        <v>10855.68769820096</v>
+        <v>334.0211599446449</v>
       </c>
     </row>
     <row r="37">
@@ -1544,19 +1308,13 @@
         <v>91350</v>
       </c>
       <c r="D37" t="n">
-        <v>58957.57855000001</v>
+        <v>6300</v>
       </c>
       <c r="E37" t="n">
-        <v>51368.592</v>
+        <v>2233.9601</v>
       </c>
       <c r="F37" t="n">
-        <v>7588.986550000003</v>
-      </c>
-      <c r="G37" t="n">
-        <v>518.9200294444447</v>
-      </c>
-      <c r="H37" t="n">
-        <v>7588.986550000003</v>
+        <v>523.3783827586209</v>
       </c>
     </row>
     <row r="38">
@@ -1572,19 +1330,13 @@
         <v>40278</v>
       </c>
       <c r="D38" t="n">
-        <v>24164.5796</v>
+        <v>5754</v>
       </c>
       <c r="E38" t="n">
-        <v>22839.0696</v>
+        <v>2301.9172</v>
       </c>
       <c r="F38" t="n">
-        <v>1325.51</v>
-      </c>
-      <c r="G38" t="n">
         <v>189.3585714285714</v>
-      </c>
-      <c r="H38" t="n">
-        <v>1325.51</v>
       </c>
     </row>
     <row r="39">
@@ -1600,19 +1352,13 @@
         <v>197100</v>
       </c>
       <c r="D39" t="n">
-        <v>109627.1587</v>
+        <v>5400</v>
       </c>
       <c r="E39" t="n">
-        <v>98512.27140000001</v>
+        <v>2396.5162</v>
       </c>
       <c r="F39" t="n">
-        <v>11114.8873</v>
-      </c>
-      <c r="G39" t="n">
         <v>304.5174602739726</v>
-      </c>
-      <c r="H39" t="n">
-        <v>11114.8873</v>
       </c>
     </row>
     <row r="40">
@@ -1628,19 +1374,13 @@
         <v>1264950</v>
       </c>
       <c r="D40" t="n">
-        <v>724008.5913000001</v>
+        <v>5856.25</v>
       </c>
       <c r="E40" t="n">
-        <v>671767.24814</v>
+        <v>2504.358373611111</v>
       </c>
       <c r="F40" t="n">
-        <v>52241.34316000005</v>
-      </c>
-      <c r="G40" t="n">
-        <v>225.2627478735834</v>
-      </c>
-      <c r="H40" t="n">
-        <v>52241.34316000005</v>
+        <v>241.8580701851854</v>
       </c>
     </row>
     <row r="41">
@@ -1656,19 +1396,13 @@
         <v>808800</v>
       </c>
       <c r="D41" t="n">
-        <v>530268.0288</v>
+        <v>5616.666666666667</v>
       </c>
       <c r="E41" t="n">
-        <v>492169.6849584236</v>
+        <v>1934.2498</v>
       </c>
       <c r="F41" t="n">
-        <v>38098.34384157638</v>
-      </c>
-      <c r="G41" t="n">
-        <v>309.3784311654777</v>
-      </c>
-      <c r="H41" t="n">
-        <v>38098.34384157638</v>
+        <v>264.5718322331693</v>
       </c>
     </row>
     <row r="42">
@@ -1684,19 +1418,13 @@
         <v>78700</v>
       </c>
       <c r="D42" t="n">
-        <v>48073.2133</v>
+        <v>5077.419354838709</v>
       </c>
       <c r="E42" t="n">
-        <v>42152.4711</v>
+        <v>1975.921722580645</v>
       </c>
       <c r="F42" t="n">
-        <v>5920.7422</v>
-      </c>
-      <c r="G42" t="n">
-        <v>380.6793850427351</v>
-      </c>
-      <c r="H42" t="n">
-        <v>5920.7422</v>
+        <v>381.9833677419355</v>
       </c>
     </row>
     <row r="43">
@@ -1712,19 +1440,13 @@
         <v>210750.94</v>
       </c>
       <c r="D43" t="n">
-        <v>120919.8086</v>
+        <v>6021.455428571428</v>
       </c>
       <c r="E43" t="n">
-        <v>110350.5789</v>
+        <v>2566.603754285714</v>
       </c>
       <c r="F43" t="n">
-        <v>10569.22970000002</v>
-      </c>
-      <c r="G43" t="n">
-        <v>294.9696388888894</v>
-      </c>
-      <c r="H43" t="n">
-        <v>10569.22970000002</v>
+        <v>301.977991428572</v>
       </c>
     </row>
     <row r="44">
@@ -1740,19 +1462,13 @@
         <v>495000</v>
       </c>
       <c r="D44" t="n">
-        <v>310687.452</v>
+        <v>5500</v>
       </c>
       <c r="E44" t="n">
-        <v>289891.4195494872</v>
+        <v>2047.9172</v>
       </c>
       <c r="F44" t="n">
-        <v>20796.03245051284</v>
-      </c>
-      <c r="G44" t="n">
-        <v>232.2073050781443</v>
-      </c>
-      <c r="H44" t="n">
-        <v>20796.03245051285</v>
+        <v>231.0670272279205</v>
       </c>
     </row>
     <row r="45">
@@ -1768,19 +1484,13 @@
         <v>78400</v>
       </c>
       <c r="D45" t="n">
-        <v>48329.1592</v>
+        <v>5600</v>
       </c>
       <c r="E45" t="n">
-        <v>44163.1424</v>
+        <v>2147.9172</v>
       </c>
       <c r="F45" t="n">
-        <v>4166.016800000003</v>
-      </c>
-      <c r="G45" t="n">
         <v>297.5726285714288</v>
-      </c>
-      <c r="H45" t="n">
-        <v>4166.016800000003</v>
       </c>
     </row>
     <row r="46">
@@ -1796,19 +1506,13 @@
         <v>39200</v>
       </c>
       <c r="D46" t="n">
-        <v>24164.5796</v>
+        <v>5600</v>
       </c>
       <c r="E46" t="n">
-        <v>24177.697</v>
+        <v>2147.9172</v>
       </c>
       <c r="F46" t="n">
-        <v>-13.11740000000373</v>
-      </c>
-      <c r="G46" t="n">
         <v>-1.873914285714818</v>
-      </c>
-      <c r="H46" t="n">
-        <v>-13.11740000000373</v>
       </c>
     </row>
     <row r="47">
@@ -1824,19 +1528,13 @@
         <v>57475</v>
       </c>
       <c r="D47" t="n">
-        <v>37921.2355</v>
+        <v>6050</v>
       </c>
       <c r="E47" t="n">
-        <v>36085.6349</v>
+        <v>2058.291</v>
       </c>
       <c r="F47" t="n">
-        <v>1835.600599999994</v>
-      </c>
-      <c r="G47" t="n">
         <v>193.2211157894731</v>
-      </c>
-      <c r="H47" t="n">
-        <v>1835.600599999994</v>
       </c>
     </row>
     <row r="48">
@@ -1852,19 +1550,13 @@
         <v>594750</v>
       </c>
       <c r="D48" t="n">
-        <v>392794.3975000001</v>
+        <v>6007.575757575758</v>
       </c>
       <c r="E48" t="n">
-        <v>341411.569659897</v>
+        <v>2039.95558080808</v>
       </c>
       <c r="F48" t="n">
-        <v>51382.82784010306</v>
-      </c>
-      <c r="G48" t="n">
-        <v>544.2502157111072</v>
-      </c>
-      <c r="H48" t="n">
-        <v>51382.82784010305</v>
+        <v>519.018463031344</v>
       </c>
     </row>
     <row r="49">
@@ -1880,19 +1572,13 @@
         <v>131100</v>
       </c>
       <c r="D49" t="n">
-        <v>79397.9044</v>
+        <v>5700</v>
       </c>
       <c r="E49" t="n">
-        <v>74469.3229</v>
+        <v>2247.9172</v>
       </c>
       <c r="F49" t="n">
-        <v>4928.58150000001</v>
-      </c>
-      <c r="G49" t="n">
-        <v>206.9671700952385</v>
-      </c>
-      <c r="H49" t="n">
-        <v>4928.58150000001</v>
+        <v>214.2861521739135</v>
       </c>
     </row>
     <row r="50">
@@ -1908,19 +1594,13 @@
         <v>162542.24</v>
       </c>
       <c r="D50" t="n">
-        <v>96658.3184</v>
+        <v>5805.08</v>
       </c>
       <c r="E50" t="n">
-        <v>90125.01899253426</v>
+        <v>2352.9972</v>
       </c>
       <c r="F50" t="n">
-        <v>6533.299407465738</v>
-      </c>
-      <c r="G50" t="n">
-        <v>198.6320461301366</v>
-      </c>
-      <c r="H50" t="n">
-        <v>6533.299407465738</v>
+        <v>233.3321216952049</v>
       </c>
     </row>
     <row r="51">
@@ -1936,19 +1616,13 @@
         <v>1170000</v>
       </c>
       <c r="D51" t="n">
-        <v>744546</v>
+        <v>5850</v>
       </c>
       <c r="E51" t="n">
-        <v>647583.0277884973</v>
+        <v>2127.27</v>
       </c>
       <c r="F51" t="n">
-        <v>96962.9722115027</v>
-      </c>
-      <c r="G51" t="n">
-        <v>447.4214110689794</v>
-      </c>
-      <c r="H51" t="n">
-        <v>96962.97221150268</v>
+        <v>484.8148610575134</v>
       </c>
     </row>
     <row r="52">
@@ -1964,19 +1638,13 @@
         <v>384750</v>
       </c>
       <c r="D52" t="n">
-        <v>251129.025</v>
+        <v>5700</v>
       </c>
       <c r="E52" t="n">
-        <v>235686.7088908389</v>
+        <v>1979.57</v>
       </c>
       <c r="F52" t="n">
-        <v>15442.31610916112</v>
-      </c>
-      <c r="G52" t="n">
-        <v>230.9079071623308</v>
-      </c>
-      <c r="H52" t="n">
-        <v>15442.31610916112</v>
+        <v>228.7750534690536</v>
       </c>
     </row>
     <row r="53">
@@ -1992,19 +1660,13 @@
         <v>38600</v>
       </c>
       <c r="D53" t="n">
-        <v>21921.5846</v>
+        <v>5514.285714285715</v>
       </c>
       <c r="E53" t="n">
-        <v>19581.87736666666</v>
+        <v>2382.630771428571</v>
       </c>
       <c r="F53" t="n">
-        <v>2339.707233333343</v>
-      </c>
-      <c r="G53" t="n">
-        <v>315.253463333335</v>
-      </c>
-      <c r="H53" t="n">
-        <v>2339.707233333343</v>
+        <v>334.2438904761919</v>
       </c>
     </row>
     <row r="54">
@@ -2020,19 +1682,13 @@
         <v>579300</v>
       </c>
       <c r="D54" t="n">
-        <v>392406.99</v>
+        <v>6034.375</v>
       </c>
       <c r="E54" t="n">
-        <v>344181.7186</v>
+        <v>1946.802187499999</v>
       </c>
       <c r="F54" t="n">
-        <v>48225.27140000006</v>
-      </c>
-      <c r="G54" t="n">
-        <v>584.7909154229581</v>
-      </c>
-      <c r="H54" t="n">
-        <v>48225.27140000005</v>
+        <v>502.3465770833338</v>
       </c>
     </row>
     <row r="55">
@@ -2048,19 +1704,13 @@
         <v>2682600</v>
       </c>
       <c r="D55" t="n">
-        <v>1787403.0703</v>
+        <v>5889.352360043908</v>
       </c>
       <c r="E55" t="n">
-        <v>1591805.156457027</v>
+        <v>1965.306102524698</v>
       </c>
       <c r="F55" t="n">
-        <v>195597.9138429729</v>
-      </c>
-      <c r="G55" t="n">
-        <v>423.3445813509851</v>
-      </c>
-      <c r="H55" t="n">
-        <v>195597.9138429729</v>
+        <v>429.4136418067462</v>
       </c>
     </row>
   </sheetData>
@@ -2074,7 +1724,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2090,32 +1740,17 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>total_revenue</t>
+          <t>avg_grade</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>total_customer_mix_cost</t>
+          <t>avg_rm_cost_per_m3</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>total_optimized_mix_cost</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>total_savings</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>avg_savings_per_cum</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>savings_per_cum</t>
+          <t>avg_mix_cost</t>
         </is>
       </c>
     </row>
@@ -2129,22 +1764,13 @@
         <v>184</v>
       </c>
       <c r="C2" t="n">
-        <v>975900</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>552260.1617000001</v>
+        <v>2663.2471475</v>
       </c>
       <c r="E2" t="n">
-        <v>490037.47514</v>
-      </c>
-      <c r="F2" t="n">
-        <v>62222.68656000007</v>
-      </c>
-      <c r="G2" t="n">
-        <v>343.2764671265665</v>
-      </c>
-      <c r="H2" t="n">
-        <v>62222.68656000007</v>
+        <v>2663.2471475</v>
       </c>
     </row>
     <row r="3">
@@ -2157,22 +1783,13 @@
         <v>299</v>
       </c>
       <c r="C3" t="n">
-        <v>1568550</v>
+        <v>15</v>
       </c>
       <c r="D3" t="n">
-        <v>1000902.1878</v>
+        <v>2933.581977591973</v>
       </c>
       <c r="E3" t="n">
-        <v>877141.0113</v>
-      </c>
-      <c r="F3" t="n">
-        <v>123761.1765</v>
-      </c>
-      <c r="G3" t="n">
-        <v>420.6885302600413</v>
-      </c>
-      <c r="H3" t="n">
-        <v>123761.1765</v>
+        <v>2933.581977591973</v>
       </c>
     </row>
     <row r="4">
@@ -2185,22 +1802,13 @@
         <v>246.5</v>
       </c>
       <c r="C4" t="n">
-        <v>1436100</v>
+        <v>20</v>
       </c>
       <c r="D4" t="n">
-        <v>835231.618</v>
+        <v>3142.052838539554</v>
       </c>
       <c r="E4" t="n">
-        <v>774516.0247000001</v>
-      </c>
-      <c r="F4" t="n">
-        <v>60715.59330000004</v>
-      </c>
-      <c r="G4" t="n">
-        <v>242.5724555335471</v>
-      </c>
-      <c r="H4" t="n">
-        <v>60715.59330000005</v>
+        <v>3142.052838539554</v>
       </c>
     </row>
     <row r="5">
@@ -2213,22 +1821,13 @@
         <v>1126</v>
       </c>
       <c r="C5" t="n">
-        <v>6443870.24</v>
+        <v>25</v>
       </c>
       <c r="D5" t="n">
-        <v>3967062.7055</v>
+        <v>3215.570636669364</v>
       </c>
       <c r="E5" t="n">
-        <v>3620732.536889703</v>
-      </c>
-      <c r="F5" t="n">
-        <v>346330.1686102967</v>
-      </c>
-      <c r="G5" t="n">
-        <v>266.731874925109</v>
-      </c>
-      <c r="H5" t="n">
-        <v>346330.1686102967</v>
+        <v>3215.570636669364</v>
       </c>
     </row>
     <row r="6">
@@ -2241,22 +1840,13 @@
         <v>2133.5</v>
       </c>
       <c r="C6" t="n">
-        <v>12541610.85</v>
+        <v>30</v>
       </c>
       <c r="D6" t="n">
-        <v>8127424.792900001</v>
+        <v>3480.578646283669</v>
       </c>
       <c r="E6" t="n">
-        <v>7425814.541846207</v>
-      </c>
-      <c r="F6" t="n">
-        <v>701610.2510537925</v>
-      </c>
-      <c r="G6" t="n">
-        <v>321.2646850852326</v>
-      </c>
-      <c r="H6" t="n">
-        <v>701610.2510537925</v>
+        <v>3480.578646283669</v>
       </c>
     </row>
     <row r="7">
@@ -2269,22 +1859,13 @@
         <v>225</v>
       </c>
       <c r="C7" t="n">
-        <v>1344350</v>
+        <v>35</v>
       </c>
       <c r="D7" t="n">
-        <v>859710.98765</v>
+        <v>3587.164084444445</v>
       </c>
       <c r="E7" t="n">
-        <v>807111.919</v>
-      </c>
-      <c r="F7" t="n">
-        <v>52599.06865</v>
-      </c>
-      <c r="G7" t="n">
-        <v>289.4424670656152</v>
-      </c>
-      <c r="H7" t="n">
-        <v>52599.06865</v>
+        <v>3587.164084444445</v>
       </c>
     </row>
     <row r="8">
@@ -2297,22 +1878,13 @@
         <v>24</v>
       </c>
       <c r="C8" t="n">
-        <v>148800</v>
+        <v>35</v>
       </c>
       <c r="D8" t="n">
-        <v>101410.92</v>
+        <v>3786.151995833333</v>
       </c>
       <c r="E8" t="n">
-        <v>90867.6479</v>
-      </c>
-      <c r="F8" t="n">
-        <v>10543.2721</v>
-      </c>
-      <c r="G8" t="n">
-        <v>439.3030041666666</v>
-      </c>
-      <c r="H8" t="n">
-        <v>10543.2721</v>
+        <v>3786.151995833333</v>
       </c>
     </row>
     <row r="9">
@@ -2325,22 +1897,13 @@
         <v>37.5</v>
       </c>
       <c r="C9" t="n">
-        <v>226875</v>
+        <v>40</v>
       </c>
       <c r="D9" t="n">
-        <v>152266.2635</v>
+        <v>3712.397232</v>
       </c>
       <c r="E9" t="n">
-        <v>139214.8962</v>
-      </c>
-      <c r="F9" t="n">
-        <v>13051.36729999998</v>
-      </c>
-      <c r="G9" t="n">
-        <v>296.8921061090221</v>
-      </c>
-      <c r="H9" t="n">
-        <v>13051.36729999998</v>
+        <v>3712.397232</v>
       </c>
     </row>
     <row r="10">
@@ -2353,22 +1916,13 @@
         <v>152</v>
       </c>
       <c r="C10" t="n">
-        <v>1003200</v>
+        <v>50</v>
       </c>
       <c r="D10" t="n">
-        <v>667293.6799999999</v>
+        <v>4249.676440789473</v>
       </c>
       <c r="E10" t="n">
-        <v>645950.8190000001</v>
-      </c>
-      <c r="F10" t="n">
-        <v>21342.86099999994</v>
-      </c>
-      <c r="G10" t="n">
-        <v>126.2891379260993</v>
-      </c>
-      <c r="H10" t="n">
-        <v>21342.86099999995</v>
+        <v>4249.676440789473</v>
       </c>
     </row>
     <row r="11">
@@ -2381,22 +1935,13 @@
         <v>6</v>
       </c>
       <c r="C11" t="n">
-        <v>27600</v>
+        <v>7</v>
       </c>
       <c r="D11" t="n">
-        <v>17726.82</v>
+        <v>2520.891633333333</v>
       </c>
       <c r="E11" t="n">
-        <v>15125.3498</v>
-      </c>
-      <c r="F11" t="n">
-        <v>2601.470200000002</v>
-      </c>
-      <c r="G11" t="n">
-        <v>433.5783666666671</v>
-      </c>
-      <c r="H11" t="n">
-        <v>2601.470200000002</v>
+        <v>2520.891633333333</v>
       </c>
     </row>
   </sheetData>
@@ -2410,7 +1955,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BO254"/>
+  <dimension ref="A1:BP254"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2749,6 +2294,11 @@
           <t>saving_per_cum</t>
         </is>
       </c>
+      <c r="BP1" s="1" t="inlineStr">
+        <is>
+          <t>grade_num</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
@@ -2960,6 +2510,9 @@
       <c r="BO2" t="n">
         <v>351.0641500000002</v>
       </c>
+      <c r="BP2" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -3171,6 +2724,9 @@
       <c r="BO3" t="n">
         <v>677.5643999999993</v>
       </c>
+      <c r="BP3" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -3382,6 +2938,9 @@
       <c r="BO4" t="n">
         <v>879.5480285714279</v>
       </c>
+      <c r="BP4" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -3593,6 +3152,9 @@
       <c r="BO5" t="n">
         <v>336.0628428571431</v>
       </c>
+      <c r="BP5" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -3804,6 +3366,9 @@
       <c r="BO6" t="n">
         <v>129.1653567567569</v>
       </c>
+      <c r="BP6" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -4015,6 +3580,9 @@
       <c r="BO7" t="n">
         <v>198.9178000000006</v>
       </c>
+      <c r="BP7" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -4226,6 +3794,9 @@
       <c r="BO8" t="n">
         <v>564.7071790697682</v>
       </c>
+      <c r="BP8" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -4437,6 +4008,9 @@
       <c r="BO9" t="n">
         <v>84.39825000000019</v>
       </c>
+      <c r="BP9" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -4648,6 +4222,9 @@
       <c r="BO10" t="n">
         <v>344.2062090909094</v>
       </c>
+      <c r="BP10" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -4859,6 +4436,9 @@
       <c r="BO11" t="n">
         <v>267.1054333333336</v>
       </c>
+      <c r="BP11" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -5070,6 +4650,9 @@
       <c r="BO12" t="n">
         <v>270.9424666666691</v>
       </c>
+      <c r="BP12" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -5281,6 +4864,9 @@
       <c r="BO13" t="n">
         <v>270.9424666666673</v>
       </c>
+      <c r="BP13" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -5492,6 +5078,9 @@
       <c r="BO14" t="n">
         <v>220.6249052631583</v>
       </c>
+      <c r="BP14" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -5703,6 +5292,9 @@
       <c r="BO15" t="n">
         <v>749.2255052631581</v>
       </c>
+      <c r="BP15" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -5914,6 +5506,9 @@
       <c r="BO16" t="n">
         <v>60.81766666666636</v>
       </c>
+      <c r="BP16" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -6125,6 +5720,9 @@
       <c r="BO17" t="n">
         <v>99.76525000000038</v>
       </c>
+      <c r="BP17" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
@@ -6336,6 +5934,9 @@
       <c r="BO18" t="n">
         <v>343.6084700000001</v>
       </c>
+      <c r="BP18" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -6547,6 +6148,9 @@
       <c r="BO19" t="n">
         <v>393.2426700000001</v>
       </c>
+      <c r="BP19" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
@@ -6758,6 +6362,9 @@
       <c r="BO20" t="n">
         <v>129.2318950000003</v>
       </c>
+      <c r="BP20" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
@@ -6969,6 +6576,9 @@
       <c r="BO21" t="n">
         <v>268.0321972602737</v>
       </c>
+      <c r="BP21" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
@@ -7180,6 +6790,9 @@
       <c r="BO22" t="n">
         <v>129.2318949999999</v>
       </c>
+      <c r="BP22" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
@@ -7391,6 +7004,9 @@
       <c r="BO23" t="n">
         <v>268.0321972602733</v>
       </c>
+      <c r="BP23" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
@@ -7602,6 +7218,9 @@
       <c r="BO24" t="n">
         <v>230.8180888888892</v>
       </c>
+      <c r="BP24" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
@@ -7813,6 +7432,9 @@
       <c r="BO25" t="n">
         <v>308.0786706467657</v>
       </c>
+      <c r="BP25" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
@@ -8024,6 +7646,9 @@
       <c r="BO26" t="n">
         <v>320.6113200000004</v>
       </c>
+      <c r="BP26" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
@@ -8235,6 +7860,9 @@
       <c r="BO27" t="n">
         <v>266.7764833333326</v>
       </c>
+      <c r="BP27" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
@@ -8446,6 +8074,9 @@
       <c r="BO28" t="n">
         <v>312.7236799999996</v>
       </c>
+      <c r="BP28" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
@@ -8657,6 +8288,9 @@
       <c r="BO29" t="n">
         <v>405.3174479591839</v>
       </c>
+      <c r="BP29" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
@@ -8868,6 +8502,9 @@
       <c r="BO30" t="n">
         <v>460.604616666667</v>
       </c>
+      <c r="BP30" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
@@ -9079,6 +8716,9 @@
       <c r="BO31" t="n">
         <v>363.4621600000005</v>
       </c>
+      <c r="BP31" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
@@ -9290,6 +8930,9 @@
       <c r="BO32" t="n">
         <v>292.4061550000006</v>
       </c>
+      <c r="BP32" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
@@ -9501,6 +9144,9 @@
       <c r="BO33" t="n">
         <v>373.6855550000009</v>
       </c>
+      <c r="BP33" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
@@ -9712,6 +9358,9 @@
       <c r="BO34" t="n">
         <v>-1.873914285714818</v>
       </c>
+      <c r="BP34" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
@@ -9923,6 +9572,9 @@
       <c r="BO35" t="n">
         <v>381.3867</v>
       </c>
+      <c r="BP35" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
@@ -10134,6 +9786,9 @@
       <c r="BO36" t="n">
         <v>491.6456499999999</v>
       </c>
+      <c r="BP36" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
@@ -10345,6 +10000,9 @@
       <c r="BO37" t="n">
         <v>403.1095720000003</v>
       </c>
+      <c r="BP37" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
@@ -10556,6 +10214,9 @@
       <c r="BO38" t="n">
         <v>287.8630235294117</v>
       </c>
+      <c r="BP38" t="n">
+        <v>35</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
@@ -10767,6 +10428,9 @@
       <c r="BO39" t="n">
         <v>352.0405384615392</v>
       </c>
+      <c r="BP39" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
@@ -10978,6 +10642,9 @@
       <c r="BO40" t="n">
         <v>352.0405384615387</v>
       </c>
+      <c r="BP40" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
@@ -11189,6 +10856,9 @@
       <c r="BO41" t="n">
         <v>368.2582386363642</v>
       </c>
+      <c r="BP41" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
@@ -11400,6 +11070,9 @@
       <c r="BO42" t="n">
         <v>280.1219583333336</v>
       </c>
+      <c r="BP42" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
@@ -11611,6 +11284,9 @@
       <c r="BO43" t="n">
         <v>396.9304074074075</v>
       </c>
+      <c r="BP43" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
@@ -11822,6 +11498,9 @@
       <c r="BO44" t="n">
         <v>525.6030074074074</v>
       </c>
+      <c r="BP44" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
@@ -12033,6 +11712,9 @@
       <c r="BO45" t="n">
         <v>366.1152833333322</v>
       </c>
+      <c r="BP45" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
@@ -12244,6 +11926,9 @@
       <c r="BO46" t="n">
         <v>497.6559000000002</v>
       </c>
+      <c r="BP46" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
@@ -12455,6 +12140,9 @@
       <c r="BO47" t="n">
         <v>223.4418307692308</v>
       </c>
+      <c r="BP47" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
@@ -12666,6 +12354,9 @@
       <c r="BO48" t="n">
         <v>433.5783666666671</v>
       </c>
+      <c r="BP48" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
@@ -12877,6 +12568,9 @@
       <c r="BO49" t="n">
         <v>387.5445111111117</v>
       </c>
+      <c r="BP49" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
@@ -13088,6 +12782,9 @@
       <c r="BO50" t="n">
         <v>465.2767111111107</v>
       </c>
+      <c r="BP50" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
@@ -13299,6 +12996,9 @@
       <c r="BO51" t="n">
         <v>114.4138256410261</v>
       </c>
+      <c r="BP51" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
@@ -13510,6 +13210,9 @@
       <c r="BO52" t="n">
         <v>351.1924125</v>
       </c>
+      <c r="BP52" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
@@ -13721,6 +13424,9 @@
       <c r="BO53" t="n">
         <v>490.1725578947367</v>
       </c>
+      <c r="BP53" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
@@ -13932,6 +13638,9 @@
       <c r="BO54" t="n">
         <v>177.1975578947377</v>
       </c>
+      <c r="BP54" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
@@ -14143,6 +13852,9 @@
       <c r="BO55" t="n">
         <v>400.4039250000001</v>
       </c>
+      <c r="BP55" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
@@ -14354,6 +14066,9 @@
       <c r="BO56" t="n">
         <v>615.8880021276595</v>
       </c>
+      <c r="BP56" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
@@ -14565,6 +14280,9 @@
       <c r="BO57" t="n">
         <v>225.9240030303031</v>
       </c>
+      <c r="BP57" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
@@ -14776,6 +14494,9 @@
       <c r="BO58" t="n">
         <v>502.2474099999999</v>
       </c>
+      <c r="BP58" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
@@ -14987,6 +14708,9 @@
       <c r="BO59" t="n">
         <v>154.7854754098353</v>
       </c>
+      <c r="BP59" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
@@ -15198,6 +14922,9 @@
       <c r="BO60" t="n">
         <v>386.8868777777789</v>
       </c>
+      <c r="BP60" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
@@ -15409,6 +15136,9 @@
       <c r="BO61" t="n">
         <v>324.2027904761903</v>
       </c>
+      <c r="BP61" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
@@ -15620,6 +15350,9 @@
       <c r="BO62" t="n">
         <v>324.2027904761912</v>
       </c>
+      <c r="BP62" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
@@ -15831,6 +15564,9 @@
       <c r="BO63" t="n">
         <v>126.9548722222221</v>
       </c>
+      <c r="BP63" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
@@ -16042,6 +15778,9 @@
       <c r="BO64" t="n">
         <v>619.5897333333332</v>
       </c>
+      <c r="BP64" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
@@ -16253,6 +15992,9 @@
       <c r="BO65" t="n">
         <v>98.52647692307664</v>
       </c>
+      <c r="BP65" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
@@ -16464,6 +16206,9 @@
       <c r="BO66" t="n">
         <v>504.5800769230773</v>
       </c>
+      <c r="BP66" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
@@ -16675,6 +16420,9 @@
       <c r="BO67" t="n">
         <v>164.1970000000001</v>
       </c>
+      <c r="BP67" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
@@ -16886,6 +16634,9 @@
       <c r="BO68" t="n">
         <v>304.5174602739726</v>
       </c>
+      <c r="BP68" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
@@ -17097,6 +16848,9 @@
       <c r="BO69" t="n">
         <v>393.2023255813956</v>
       </c>
+      <c r="BP69" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
@@ -17308,6 +17062,9 @@
       <c r="BO70" t="n">
         <v>291.1354640000004</v>
       </c>
+      <c r="BP70" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
@@ -17519,6 +17276,9 @@
       <c r="BO71" t="n">
         <v>122.7988761904767</v>
       </c>
+      <c r="BP71" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
@@ -17730,6 +17490,9 @@
       <c r="BO72" t="n">
         <v>310.9445500000006</v>
       </c>
+      <c r="BP72" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
@@ -17941,6 +17704,9 @@
       <c r="BO73" t="n">
         <v>359.176366666667</v>
       </c>
+      <c r="BP73" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
@@ -18152,6 +17918,9 @@
       <c r="BO74" t="n">
         <v>530.6738700000001</v>
       </c>
+      <c r="BP74" t="n">
+        <v>35</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
@@ -18363,6 +18132,9 @@
       <c r="BO75" t="n">
         <v>165.0812000000005</v>
       </c>
+      <c r="BP75" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
@@ -18574,6 +18346,9 @@
       <c r="BO76" t="n">
         <v>391.6567476190476</v>
       </c>
+      <c r="BP76" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
@@ -18785,6 +18560,9 @@
       <c r="BO77" t="n">
         <v>287.1065166666667</v>
       </c>
+      <c r="BP77" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
@@ -18996,6 +18774,9 @@
       <c r="BO78" t="n">
         <v>292.4480201550382</v>
       </c>
+      <c r="BP78" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
@@ -19207,6 +18988,9 @@
       <c r="BO79" t="n">
         <v>563.095220155039</v>
       </c>
+      <c r="BP79" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
@@ -19418,6 +19202,9 @@
       <c r="BO80" t="n">
         <v>286.3617114285712</v>
       </c>
+      <c r="BP80" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
@@ -19629,6 +19416,9 @@
       <c r="BO81" t="n">
         <v>242.703836666667</v>
       </c>
+      <c r="BP81" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
@@ -19840,6 +19630,9 @@
       <c r="BO82" t="n">
         <v>503.5697749999999</v>
       </c>
+      <c r="BP82" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
@@ -20051,6 +19844,9 @@
       <c r="BO83" t="n">
         <v>135.4879999999994</v>
       </c>
+      <c r="BP83" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
@@ -20262,6 +20058,9 @@
       <c r="BO84" t="n">
         <v>389.8017249999998</v>
       </c>
+      <c r="BP84" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
@@ -20473,6 +20272,9 @@
       <c r="BO85" t="n">
         <v>291.3596173076926</v>
       </c>
+      <c r="BP85" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
@@ -20684,6 +20486,9 @@
       <c r="BO86" t="n">
         <v>546.360217307692</v>
       </c>
+      <c r="BP86" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
@@ -20895,6 +20700,9 @@
       <c r="BO87" t="n">
         <v>331.2375088435374</v>
       </c>
+      <c r="BP87" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
@@ -21106,6 +20914,9 @@
       <c r="BO88" t="n">
         <v>889.2161088435387</v>
       </c>
+      <c r="BP88" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
@@ -21317,6 +21128,9 @@
       <c r="BO89" t="n">
         <v>407.163656666668</v>
       </c>
+      <c r="BP89" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
@@ -21528,6 +21342,9 @@
       <c r="BO90" t="n">
         <v>432.6667000000002</v>
       </c>
+      <c r="BP90" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
@@ -21739,6 +21556,9 @@
       <c r="BO91" t="n">
         <v>124.9792222222231</v>
       </c>
+      <c r="BP91" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
@@ -21950,6 +21770,9 @@
       <c r="BO92" t="n">
         <v>386.9965000000002</v>
       </c>
+      <c r="BP92" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
@@ -22161,6 +21984,9 @@
       <c r="BO93" t="n">
         <v>115.967698360656</v>
       </c>
+      <c r="BP93" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
@@ -22372,6 +22198,9 @@
       <c r="BO94" t="n">
         <v>321.2555057591626</v>
       </c>
+      <c r="BP94" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
@@ -22583,6 +22412,9 @@
       <c r="BO95" t="n">
         <v>11.04353333333347</v>
       </c>
+      <c r="BP95" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
@@ -22794,6 +22626,9 @@
       <c r="BO96" t="n">
         <v>128.0312727272731</v>
       </c>
+      <c r="BP96" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
@@ -23005,6 +22840,9 @@
       <c r="BO97" t="n">
         <v>240.9160260869558</v>
       </c>
+      <c r="BP97" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
@@ -23216,6 +23054,9 @@
       <c r="BO98" t="n">
         <v>425.6639200000009</v>
       </c>
+      <c r="BP98" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
@@ -23427,6 +23268,9 @@
       <c r="BO99" t="n">
         <v>507.1661888888893</v>
       </c>
+      <c r="BP99" t="n">
+        <v>35</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
@@ -23638,6 +23482,9 @@
       <c r="BO100" t="n">
         <v>511.3793333333333</v>
       </c>
+      <c r="BP100" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
@@ -23849,6 +23696,9 @@
       <c r="BO101" t="n">
         <v>204.7253999999994</v>
       </c>
+      <c r="BP101" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
@@ -24060,6 +23910,9 @@
       <c r="BO102" t="n">
         <v>280.5406777777785</v>
       </c>
+      <c r="BP102" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
@@ -24271,6 +24124,9 @@
       <c r="BO103" t="n">
         <v>381.8805473684206</v>
       </c>
+      <c r="BP103" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
@@ -24482,6 +24338,9 @@
       <c r="BO104" t="n">
         <v>290.0990526315791</v>
       </c>
+      <c r="BP104" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
@@ -24693,6 +24552,9 @@
       <c r="BO105" t="n">
         <v>128.3595538461536</v>
       </c>
+      <c r="BP105" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
@@ -24904,6 +24766,9 @@
       <c r="BO106" t="n">
         <v>189.3585714285714</v>
       </c>
+      <c r="BP106" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
@@ -25115,6 +24980,9 @@
       <c r="BO107" t="n">
         <v>390.0672333333337</v>
       </c>
+      <c r="BP107" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
@@ -25326,6 +25194,9 @@
       <c r="BO108" t="n">
         <v>239.5938666666671</v>
       </c>
+      <c r="BP108" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
@@ -25537,6 +25408,9 @@
       <c r="BO109" t="n">
         <v>334.072533333333</v>
       </c>
+      <c r="BP109" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
@@ -25748,6 +25622,9 @@
       <c r="BO110" t="n">
         <v>384.0236000000004</v>
       </c>
+      <c r="BP110" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
@@ -25959,6 +25836,9 @@
       <c r="BO111" t="n">
         <v>386.8499166666666</v>
       </c>
+      <c r="BP111" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
@@ -26170,6 +26050,9 @@
       <c r="BO112" t="n">
         <v>614.3420600000004</v>
       </c>
+      <c r="BP112" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
@@ -26381,6 +26264,9 @@
       <c r="BO113" t="n">
         <v>212.3814181818184</v>
       </c>
+      <c r="BP113" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
@@ -26592,6 +26478,9 @@
       <c r="BO114" t="n">
         <v>472.5762681818183</v>
       </c>
+      <c r="BP114" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
@@ -26803,6 +26692,9 @@
       <c r="BO115" t="n">
         <v>604.9432681818184</v>
       </c>
+      <c r="BP115" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
@@ -27014,6 +26906,9 @@
       <c r="BO116" t="n">
         <v>392.0488666666674</v>
       </c>
+      <c r="BP116" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
@@ -27225,6 +27120,9 @@
       <c r="BO117" t="n">
         <v>338.1375199999998</v>
       </c>
+      <c r="BP117" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
@@ -27436,6 +27334,9 @@
       <c r="BO118" t="n">
         <v>62.33281333333298</v>
       </c>
+      <c r="BP118" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
@@ -27647,6 +27548,9 @@
       <c r="BO119" t="n">
         <v>484.6434133333332</v>
       </c>
+      <c r="BP119" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
@@ -27858,6 +27762,9 @@
       <c r="BO120" t="n">
         <v>250.3872000000006</v>
       </c>
+      <c r="BP120" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
@@ -28069,6 +27976,9 @@
       <c r="BO121" t="n">
         <v>130.357535294118</v>
       </c>
+      <c r="BP121" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
@@ -28280,6 +28190,9 @@
       <c r="BO122" t="n">
         <v>327.5137500000005</v>
       </c>
+      <c r="BP122" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
@@ -28491,6 +28404,9 @@
       <c r="BO123" t="n">
         <v>123.8685903846158</v>
       </c>
+      <c r="BP123" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
@@ -28702,6 +28618,9 @@
       <c r="BO124" t="n">
         <v>357.5584380952382</v>
       </c>
+      <c r="BP124" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
@@ -28913,6 +28832,9 @@
       <c r="BO125" t="n">
         <v>123.8685903846153</v>
       </c>
+      <c r="BP125" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
@@ -29124,6 +29046,9 @@
       <c r="BO126" t="n">
         <v>123.8685903846153</v>
       </c>
+      <c r="BP126" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
@@ -29335,6 +29260,9 @@
       <c r="BO127" t="n">
         <v>357.5584380952382</v>
       </c>
+      <c r="BP127" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
@@ -29546,6 +29474,9 @@
       <c r="BO128" t="n">
         <v>379.3290965517235</v>
       </c>
+      <c r="BP128" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">
@@ -29757,6 +29688,9 @@
       <c r="BO129" t="n">
         <v>379.329096551724</v>
       </c>
+      <c r="BP129" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
@@ -29968,6 +29902,9 @@
       <c r="BO130" t="n">
         <v>118.8001692307694</v>
       </c>
+      <c r="BP130" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="n">
@@ -30179,6 +30116,9 @@
       <c r="BO131" t="n">
         <v>322.2575188679243</v>
       </c>
+      <c r="BP131" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="n">
@@ -30390,6 +30330,9 @@
       <c r="BO132" t="n">
         <v>322.2575188679248</v>
       </c>
+      <c r="BP132" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="n">
@@ -30601,6 +30544,9 @@
       <c r="BO133" t="n">
         <v>403.5369188679256</v>
       </c>
+      <c r="BP133" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="n">
@@ -30812,6 +30758,9 @@
       <c r="BO134" t="n">
         <v>209.1403565891446</v>
       </c>
+      <c r="BP134" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="n">
@@ -31023,6 +30972,9 @@
       <c r="BO135" t="n">
         <v>290.3599565891454</v>
       </c>
+      <c r="BP135" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="n">
@@ -31234,6 +31186,9 @@
       <c r="BO136" t="n">
         <v>165.244006976744</v>
       </c>
+      <c r="BP136" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="n">
@@ -31445,6 +31400,9 @@
       <c r="BO137" t="n">
         <v>177.1030069767439</v>
       </c>
+      <c r="BP137" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="n">
@@ -31656,6 +31614,9 @@
       <c r="BO138" t="n">
         <v>116.2981576923075</v>
       </c>
+      <c r="BP138" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="n">
@@ -31867,6 +31828,9 @@
       <c r="BO139" t="n">
         <v>282.6361550000001</v>
       </c>
+      <c r="BP139" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="n">
@@ -32078,6 +32042,9 @@
       <c r="BO140" t="n">
         <v>386.9453576923074</v>
       </c>
+      <c r="BP140" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="n">
@@ -32289,6 +32256,9 @@
       <c r="BO141" t="n">
         <v>553.283355</v>
       </c>
+      <c r="BP141" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="n">
@@ -32500,6 +32470,9 @@
       <c r="BO142" t="n">
         <v>215.8744744186047</v>
       </c>
+      <c r="BP142" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="n">
@@ -32711,6 +32684,9 @@
       <c r="BO143" t="n">
         <v>200.1172744186042</v>
       </c>
+      <c r="BP143" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="n">
@@ -32922,6 +32898,9 @@
       <c r="BO144" t="n">
         <v>55.03425749999997</v>
       </c>
+      <c r="BP144" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="n">
@@ -33133,6 +33112,9 @@
       <c r="BO145" t="n">
         <v>323.2796777777776</v>
       </c>
+      <c r="BP145" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="n">
@@ -33344,6 +33326,9 @@
       <c r="BO146" t="n">
         <v>287.8089500000001</v>
       </c>
+      <c r="BP146" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="n">
@@ -33555,6 +33540,9 @@
       <c r="BO147" t="n">
         <v>109.9853933333338</v>
       </c>
+      <c r="BP147" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="n">
@@ -33766,6 +33754,9 @@
       <c r="BO148" t="n">
         <v>188.9479346153844</v>
       </c>
+      <c r="BP148" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="n">
@@ -33977,6 +33968,9 @@
       <c r="BO149" t="n">
         <v>324.7934</v>
       </c>
+      <c r="BP149" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="n">
@@ -34188,6 +34182,9 @@
       <c r="BO150" t="n">
         <v>464.8235346153851</v>
       </c>
+      <c r="BP150" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="n">
@@ -34399,6 +34396,9 @@
       <c r="BO151" t="n">
         <v>763.1835346153857</v>
       </c>
+      <c r="BP151" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="n">
@@ -34610,6 +34610,9 @@
       <c r="BO152" t="n">
         <v>184.2078274509804</v>
       </c>
+      <c r="BP152" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="n">
@@ -34821,6 +34824,9 @@
       <c r="BO153" t="n">
         <v>135.4176666666672</v>
       </c>
+      <c r="BP153" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="n">
@@ -35032,6 +35038,9 @@
       <c r="BO154" t="n">
         <v>359.564460000001</v>
       </c>
+      <c r="BP154" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="n">
@@ -35243,6 +35252,9 @@
       <c r="BO155" t="n">
         <v>399.1818333333335</v>
       </c>
+      <c r="BP155" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="n">
@@ -35454,6 +35466,9 @@
       <c r="BO156" t="n">
         <v>291.2517857142857</v>
       </c>
+      <c r="BP156" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="n">
@@ -35665,6 +35680,9 @@
       <c r="BO157" t="n">
         <v>118.308610526316</v>
       </c>
+      <c r="BP157" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="n">
@@ -35876,6 +35894,9 @@
       <c r="BO158" t="n">
         <v>192.4524989473689</v>
       </c>
+      <c r="BP158" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="n">
@@ -36087,6 +36108,9 @@
       <c r="BO159" t="n">
         <v>331.2919461538468</v>
       </c>
+      <c r="BP159" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="n">
@@ -36298,6 +36322,9 @@
       <c r="BO160" t="n">
         <v>208.7094989473685</v>
       </c>
+      <c r="BP160" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="n">
@@ -36509,6 +36536,9 @@
       <c r="BO161" t="n">
         <v>192.9522989473685</v>
       </c>
+      <c r="BP161" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="n">
@@ -36720,6 +36750,9 @@
       <c r="BO162" t="n">
         <v>60.85055263157892</v>
       </c>
+      <c r="BP162" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="n">
@@ -36931,6 +36964,9 @@
       <c r="BO163" t="n">
         <v>63.40415249999978</v>
       </c>
+      <c r="BP163" t="n">
+        <v>35</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="n">
@@ -37142,6 +37178,9 @@
       <c r="BO164" t="n">
         <v>282.1104999999993</v>
       </c>
+      <c r="BP164" t="n">
+        <v>35</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="n">
@@ -37353,6 +37392,9 @@
       <c r="BO165" t="n">
         <v>439.3030041666666</v>
       </c>
+      <c r="BP165" t="n">
+        <v>35</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="n">
@@ -37564,6 +37606,9 @@
       <c r="BO166" t="n">
         <v>73.27450000000044</v>
       </c>
+      <c r="BP166" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="n">
@@ -37775,6 +37820,9 @@
       <c r="BO167" t="n">
         <v>368.418714285714</v>
       </c>
+      <c r="BP167" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="n">
@@ -37986,6 +38034,9 @@
       <c r="BO168" t="n">
         <v>122.1524850000001</v>
       </c>
+      <c r="BP168" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="n">
@@ -38197,6 +38248,9 @@
       <c r="BO169" t="n">
         <v>296.9158721311478</v>
       </c>
+      <c r="BP169" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="n">
@@ -38408,6 +38462,9 @@
       <c r="BO170" t="n">
         <v>123.5646666666667</v>
       </c>
+      <c r="BP170" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="n">
@@ -38619,6 +38676,9 @@
       <c r="BO171" t="n">
         <v>209.1527400000004</v>
       </c>
+      <c r="BP171" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="n">
@@ -38830,6 +38890,9 @@
       <c r="BO172" t="n">
         <v>476.1152833333335</v>
       </c>
+      <c r="BP172" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="n">
@@ -39041,6 +39104,9 @@
       <c r="BO173" t="n">
         <v>400.563096428571</v>
       </c>
+      <c r="BP173" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="n">
@@ -39252,6 +39318,9 @@
       <c r="BO174" t="n">
         <v>70.67559999999958</v>
       </c>
+      <c r="BP174" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="n">
@@ -39463,6 +39532,9 @@
       <c r="BO175" t="n">
         <v>566.5658057142864</v>
       </c>
+      <c r="BP175" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="n">
@@ -39674,6 +39746,9 @@
       <c r="BO176" t="n">
         <v>382.8578057142854</v>
       </c>
+      <c r="BP176" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="n">
@@ -39885,6 +39960,9 @@
       <c r="BO177" t="n">
         <v>126.8858000000005</v>
       </c>
+      <c r="BP177" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="n">
@@ -40096,6 +40174,9 @@
       <c r="BO178" t="n">
         <v>284.1500058823526</v>
       </c>
+      <c r="BP178" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="n">
@@ -40307,6 +40388,9 @@
       <c r="BO179" t="n">
         <v>284.1500058823531</v>
       </c>
+      <c r="BP179" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="n">
@@ -40518,6 +40602,9 @@
       <c r="BO180" t="n">
         <v>320.8881804878056</v>
       </c>
+      <c r="BP180" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="n">
@@ -40729,6 +40816,9 @@
       <c r="BO181" t="n">
         <v>638.4846555555569</v>
       </c>
+      <c r="BP181" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="n">
@@ -40940,6 +41030,9 @@
       <c r="BO182" t="n">
         <v>331.9834461538458</v>
       </c>
+      <c r="BP182" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="n">
@@ -41151,6 +41244,9 @@
       <c r="BO183" t="n">
         <v>125.0069999999996</v>
       </c>
+      <c r="BP183" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="n">
@@ -41362,6 +41458,9 @@
       <c r="BO184" t="n">
         <v>390.7213999999994</v>
       </c>
+      <c r="BP184" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="n">
@@ -41573,6 +41672,9 @@
       <c r="BO185" t="n">
         <v>207.7814411764703</v>
       </c>
+      <c r="BP185" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="n">
@@ -41784,6 +41886,9 @@
       <c r="BO186" t="n">
         <v>394.0867625000001</v>
       </c>
+      <c r="BP186" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="n">
@@ -41995,6 +42100,9 @@
       <c r="BO187" t="n">
         <v>113.1724888888893</v>
       </c>
+      <c r="BP187" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="n">
@@ -42206,6 +42314,9 @@
       <c r="BO188" t="n">
         <v>336.3774928571429</v>
       </c>
+      <c r="BP188" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="n">
@@ -42417,6 +42528,9 @@
       <c r="BO189" t="n">
         <v>207.7729249999998</v>
       </c>
+      <c r="BP189" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="n">
@@ -42628,6 +42742,9 @@
       <c r="BO190" t="n">
         <v>364.4271452380958</v>
       </c>
+      <c r="BP190" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="n">
@@ -42839,6 +42956,9 @@
       <c r="BO191" t="n">
         <v>632.4581018867934</v>
       </c>
+      <c r="BP191" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="n">
@@ -43050,6 +43170,9 @@
       <c r="BO192" t="n">
         <v>385.5793018867921</v>
       </c>
+      <c r="BP192" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="n">
@@ -43261,6 +43384,9 @@
       <c r="BO193" t="n">
         <v>132.7869500000002</v>
       </c>
+      <c r="BP193" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="n">
@@ -43472,6 +43598,9 @@
       <c r="BO194" t="n">
         <v>330.8642062500003</v>
       </c>
+      <c r="BP194" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="n">
@@ -43683,6 +43812,9 @@
       <c r="BO195" t="n">
         <v>746.4941866666668</v>
       </c>
+      <c r="BP195" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="n">
@@ -43894,6 +44026,9 @@
       <c r="BO196" t="n">
         <v>118.7420866666666</v>
       </c>
+      <c r="BP196" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="n">
@@ -44105,6 +44240,9 @@
       <c r="BO197" t="n">
         <v>700.0642866666667</v>
       </c>
+      <c r="BP197" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="n">
@@ -44316,6 +44454,9 @@
       <c r="BO198" t="n">
         <v>331.0480428571432</v>
       </c>
+      <c r="BP198" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="n">
@@ -44527,6 +44668,9 @@
       <c r="BO199" t="n">
         <v>109.7460307692309</v>
       </c>
+      <c r="BP199" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="n">
@@ -44738,6 +44882,9 @@
       <c r="BO200" t="n">
         <v>216.6249000000016</v>
       </c>
+      <c r="BP200" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="n">
@@ -44949,6 +45096,9 @@
       <c r="BO201" t="n">
         <v>217.2712000000006</v>
       </c>
+      <c r="BP201" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="n">
@@ -45160,6 +45310,9 @@
       <c r="BO202" t="n">
         <v>77.82759999999962</v>
       </c>
+      <c r="BP202" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="n">
@@ -45371,6 +45524,9 @@
       <c r="BO203" t="n">
         <v>140.4749999999995</v>
       </c>
+      <c r="BP203" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="n">
@@ -45582,6 +45738,9 @@
       <c r="BO204" t="n">
         <v>229.713025</v>
       </c>
+      <c r="BP204" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="n">
@@ -45793,6 +45952,9 @@
       <c r="BO205" t="n">
         <v>264.3030553191493</v>
       </c>
+      <c r="BP205" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="n">
@@ -46004,6 +46166,9 @@
       <c r="BO206" t="n">
         <v>345.5824553191496</v>
       </c>
+      <c r="BP206" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="n">
@@ -46215,6 +46380,9 @@
       <c r="BO207" t="n">
         <v>112.7804666666666</v>
       </c>
+      <c r="BP207" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="n">
@@ -46426,6 +46594,9 @@
       <c r="BO208" t="n">
         <v>102.266215384615</v>
       </c>
+      <c r="BP208" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="n">
@@ -46637,6 +46808,9 @@
       <c r="BO209" t="n">
         <v>324.2306999999996</v>
       </c>
+      <c r="BP209" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="n">
@@ -46848,6 +47022,9 @@
       <c r="BO210" t="n">
         <v>221.3680069767447</v>
       </c>
+      <c r="BP210" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="n">
@@ -47059,6 +47236,9 @@
       <c r="BO211" t="n">
         <v>12.60607999999957</v>
       </c>
+      <c r="BP211" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="n">
@@ -47270,6 +47450,9 @@
       <c r="BO212" t="n">
         <v>169.1017100000004</v>
       </c>
+      <c r="BP212" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="n">
@@ -47481,6 +47664,9 @@
       <c r="BO213" t="n">
         <v>221.4776800000009</v>
       </c>
+      <c r="BP213" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="n">
@@ -47692,6 +47878,9 @@
       <c r="BO214" t="n">
         <v>381.1651384615384</v>
       </c>
+      <c r="BP214" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="n">
@@ -47903,6 +48092,9 @@
       <c r="BO215" t="n">
         <v>-0.3963647058822062</v>
       </c>
+      <c r="BP215" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="n">
@@ -48114,6 +48306,9 @@
       <c r="BO216" t="n">
         <v>705.0426172413777</v>
       </c>
+      <c r="BP216" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="n">
@@ -48325,6 +48520,9 @@
       <c r="BO217" t="n">
         <v>243.773681818182</v>
       </c>
+      <c r="BP217" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="n">
@@ -48536,6 +48734,9 @@
       <c r="BO218" t="n">
         <v>579.1578823529417</v>
       </c>
+      <c r="BP218" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="n">
@@ -48747,6 +48948,9 @@
       <c r="BO219" t="n">
         <v>313.230922222222</v>
       </c>
+      <c r="BP219" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="n">
@@ -48958,6 +49162,9 @@
       <c r="BO220" t="n">
         <v>351.4348172413793</v>
       </c>
+      <c r="BP220" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="n">
@@ -49169,6 +49376,9 @@
       <c r="BO221" t="n">
         <v>270.1554172413789</v>
       </c>
+      <c r="BP221" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="n">
@@ -49380,6 +49590,9 @@
       <c r="BO222" t="n">
         <v>116.8477649999995</v>
       </c>
+      <c r="BP222" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="n">
@@ -49591,6 +49804,9 @@
       <c r="BO223" t="n">
         <v>112.7794333333336</v>
       </c>
+      <c r="BP223" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="n">
@@ -49802,6 +50018,9 @@
       <c r="BO224" t="n">
         <v>319.539282352941</v>
       </c>
+      <c r="BP224" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="n">
@@ -50013,6 +50232,9 @@
       <c r="BO225" t="n">
         <v>193.2211157894731</v>
       </c>
+      <c r="BP225" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="n">
@@ -50224,6 +50446,9 @@
       <c r="BO226" t="n">
         <v>128.2936666666656</v>
       </c>
+      <c r="BP226" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="n">
@@ -50435,6 +50660,9 @@
       <c r="BO227" t="n">
         <v>345.741120754717</v>
       </c>
+      <c r="BP227" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="n">
@@ -50646,6 +50874,9 @@
       <c r="BO228" t="n">
         <v>248.1721207547166</v>
       </c>
+      <c r="BP228" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="n">
@@ -50857,6 +51088,9 @@
       <c r="BO229" t="n">
         <v>240.8134428571429</v>
       </c>
+      <c r="BP229" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="n">
@@ -51068,6 +51302,9 @@
       <c r="BO230" t="n">
         <v>562.9857205128205</v>
       </c>
+      <c r="BP230" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="n">
@@ -51279,6 +51516,9 @@
       <c r="BO231" t="n">
         <v>396.4457205128215</v>
       </c>
+      <c r="BP231" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="n">
@@ -51490,6 +51730,9 @@
       <c r="BO232" t="n">
         <v>172.9751615384616</v>
       </c>
+      <c r="BP232" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="n">
@@ -51701,6 +51944,9 @@
       <c r="BO233" t="n">
         <v>161.1161615384603</v>
       </c>
+      <c r="BP233" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="n">
@@ -51912,6 +52158,9 @@
       <c r="BO234" t="n">
         <v>407.4693125000008</v>
       </c>
+      <c r="BP234" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="n">
@@ -52123,6 +52372,9 @@
       <c r="BO235" t="n">
         <v>166.2100999999993</v>
       </c>
+      <c r="BP235" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="n">
@@ -52334,6 +52586,9 @@
       <c r="BO236" t="n">
         <v>360.0287230769236</v>
       </c>
+      <c r="BP236" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="n">
@@ -52545,6 +52800,9 @@
       <c r="BO237" t="n">
         <v>394.0829250000002</v>
       </c>
+      <c r="BP237" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="n">
@@ -52756,6 +53014,9 @@
       <c r="BO238" t="n">
         <v>60.91657142857139</v>
       </c>
+      <c r="BP238" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="n">
@@ -52967,6 +53228,9 @@
       <c r="BO239" t="n">
         <v>108.6315565217392</v>
       </c>
+      <c r="BP239" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="n">
@@ -53178,6 +53442,9 @@
       <c r="BO240" t="n">
         <v>108.6315565217392</v>
       </c>
+      <c r="BP240" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="n">
@@ -53389,6 +53656,9 @@
       <c r="BO241" t="n">
         <v>106.5864888888891</v>
       </c>
+      <c r="BP241" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="n">
@@ -53600,6 +53870,9 @@
       <c r="BO242" t="n">
         <v>212.5995600000001</v>
       </c>
+      <c r="BP242" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="n">
@@ -53811,6 +54084,9 @@
       <c r="BO243" t="n">
         <v>335.1959673913047</v>
       </c>
+      <c r="BP243" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="n">
@@ -54022,6 +54298,9 @@
       <c r="BO244" t="n">
         <v>634.4482000000007</v>
       </c>
+      <c r="BP244" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="n">
@@ -54233,6 +54512,9 @@
       <c r="BO245" t="n">
         <v>80.15422692307675</v>
       </c>
+      <c r="BP245" t="n">
+        <v>35</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="n">
@@ -54444,6 +54726,9 @@
       <c r="BO246" t="n">
         <v>287.9404</v>
       </c>
+      <c r="BP246" t="n">
+        <v>35</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="n">
@@ -54655,6 +54940,9 @@
       <c r="BO247" t="n">
         <v>374.0231000000003</v>
       </c>
+      <c r="BP247" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="n">
@@ -54866,6 +55154,9 @@
       <c r="BO248" t="n">
         <v>336.0512500000004</v>
       </c>
+      <c r="BP248" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="n">
@@ -55077,6 +55368,9 @@
       <c r="BO249" t="n">
         <v>386.3386499999997</v>
       </c>
+      <c r="BP249" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="n">
@@ -55288,6 +55582,9 @@
       <c r="BO250" t="n">
         <v>273.2358636363638</v>
       </c>
+      <c r="BP250" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="n">
@@ -55499,6 +55796,9 @@
       <c r="BO251" t="n">
         <v>273.2358636363638</v>
       </c>
+      <c r="BP251" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="n">
@@ -55710,6 +56010,9 @@
       <c r="BO252" t="n">
         <v>309.3986000000004</v>
       </c>
+      <c r="BP252" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" s="2" t="n">
@@ -55921,6 +56224,9 @@
       <c r="BO253" t="n">
         <v>54.57530000000042</v>
       </c>
+      <c r="BP253" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="n">
@@ -56131,6 +56437,9 @@
       </c>
       <c r="BO254" t="n">
         <v>276.2273746835449</v>
+      </c>
+      <c r="BP254" t="n">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
